--- a/public/datos/3.1_Tabla_dinamica.xlsx
+++ b/public/datos/3.1_Tabla_dinamica.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Documentos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Enunciado_Caso" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Base_Auditoria" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Diagnostico_Dinamico" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,6 +431,168 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Sección</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Detalle del Requerimiento / Parámetros del Caso</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Código de Actividad</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Título del Caso</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Análisis multidimensional y diagnóstico SIG con Tablas Dinámicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Organización</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Lácteos del Caribe S.A.S. - Sistema Integrado de Gestión</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1. Situación Problema</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Para la Revisión por la Dirección (ISO 9001:2015), la Coordinación SIG debe diagnosticar qué macroprocesos concentran el mayor cuello de botella documental.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2. Misión del Aprendiz</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Construir una Tabla Dinámica en la hoja Diagnostico_Dinamico con jerarquía de filas, vista porcentual de filas, segmentadores de datos (Slicers) y conclusión ejecutiva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Requerimiento 1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Crear Tabla Dinámica: En hoja Diagnostico_Dinamico con origen en Base_Auditoria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Requerimiento 2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Jerarquía y Valores: Filas = 'Tipo de proceso' y 'Proceso'; Columnas = 'Estado'; Valores = Recuento de 'Código'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Requerimiento 3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Vista Porcentual: Duplicar campo de valor y configurarlo como '% del total de filas' para identificar la tasa de riesgo por proceso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Requerimiento 4</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Segmentadores Interactivos: Agregar segmentación por 'Tipo de proceso' y 'Responsable'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Requerimiento 5</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Conclusión Diagnóstica: Redactar en la celda designada cuál es el proceso más crítico y la acción preventiva propuesta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Dificultad Clave / Regla Técnica</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Configura la base de porcentaje como '% del total de filas' (no del total general) para que cada proceso sume 100% y la comparación sea rigurosa.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2087,4 +2251,106 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Paso / Elemento del Dashboard</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Instrucciones de Construcción y Entrega</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Espacio para Tabla Dinámica</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Inserta aquí la Tabla Dinámica jerárquica a partir de Base_Auditoria (rango A1:H25).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Configuración de Filas</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Nivel 1: Tipo de proceso | Nivel 2: Proceso</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Configuración de Columnas</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Campo: Estado (Vigente, Por vencer, Vencido)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Configuración de Valores</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Recuento de Código y % del total de filas</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Segmentadores de Datos</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Inserta Slicers para 'Tipo de proceso' y 'Responsable'</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Conclusión Diagnóstica</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Escribe aquí tu análisis gerencial: ¿Qué proceso requiere auditoría extraordinaria inmediata?</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>